--- a/datos/05-ejemplo-std-tecnico.xlsx
+++ b/datos/05-ejemplo-std-tecnico.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="965" documentId="8_{5F9E455A-213A-447C-A11C-7E9616724FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FF44E07-71D0-4D3A-9946-906145A9F5BF}"/>
+  <xr:revisionPtr revIDLastSave="976" documentId="8_{5F9E455A-213A-447C-A11C-7E9616724FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{748EAEC1-9256-4D88-B832-2B5A33C48AE0}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" tabRatio="675" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
+    <workbookView xWindow="3165" yWindow="885" windowWidth="23595" windowHeight="14250" tabRatio="675" xr2:uid="{6977E7F1-D64B-47FE-B2A7-D4E9B0399E18}"/>
   </bookViews>
   <sheets>
     <sheet name="Estándar técnico" sheetId="21" r:id="rId1"/>
@@ -1095,6 +1095,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="RDT (2)"/>
       <sheetName val="VERIF"/>
@@ -1509,6 +1512,9 @@
 <file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="SYNT"/>
       <sheetName val="PE"/>
